--- a/Hand_edited_log/1/student/dungtdhe186461/TC1/GradeDetail.xlsx
+++ b/Hand_edited_log/1/student/dungtdhe186461/TC1/GradeDetail.xlsx
@@ -1038,10 +1038,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P2" s="0">
-        <x:v>49679</x:v>
+        <x:v>50163</x:v>
       </x:c>
       <x:c r="Q2" s="0">
-        <x:v>4004</x:v>
+        <x:v>4005</x:v>
       </x:c>
       <x:c r="R2" s="2" t="s">
         <x:v>46</x:v>
@@ -1094,10 +1094,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P3" s="0">
-        <x:v>4004</x:v>
+        <x:v>4005</x:v>
       </x:c>
       <x:c r="Q3" s="0">
-        <x:v>49679</x:v>
+        <x:v>50163</x:v>
       </x:c>
       <x:c r="R3" s="2" t="s">
         <x:v>46</x:v>
@@ -1150,10 +1150,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P4" s="0">
-        <x:v>49679</x:v>
+        <x:v>50163</x:v>
       </x:c>
       <x:c r="Q4" s="0">
-        <x:v>4004</x:v>
+        <x:v>4005</x:v>
       </x:c>
       <x:c r="R4" s="3" t="s">
         <x:v>52</x:v>
@@ -1206,10 +1206,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P5" s="0">
-        <x:v>4004</x:v>
+        <x:v>4005</x:v>
       </x:c>
       <x:c r="Q5" s="0">
-        <x:v>49679</x:v>
+        <x:v>50163</x:v>
       </x:c>
       <x:c r="R5" s="3" t="s">
         <x:v>52</x:v>
@@ -1262,10 +1262,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P6" s="0">
-        <x:v>49679</x:v>
+        <x:v>50163</x:v>
       </x:c>
       <x:c r="Q6" s="0">
-        <x:v>4004</x:v>
+        <x:v>4005</x:v>
       </x:c>
       <x:c r="R6" s="3" t="s">
         <x:v>52</x:v>
@@ -1318,10 +1318,10 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="P7" s="0">
-        <x:v>49679</x:v>
+        <x:v>50163</x:v>
       </x:c>
       <x:c r="Q7" s="0">
-        <x:v>4004</x:v>
+        <x:v>4005</x:v>
       </x:c>
       <x:c r="R7" s="3" t="s">
         <x:v>52</x:v>
@@ -1374,10 +1374,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P8" s="0">
-        <x:v>4004</x:v>
+        <x:v>4005</x:v>
       </x:c>
       <x:c r="Q8" s="0">
-        <x:v>49679</x:v>
+        <x:v>50163</x:v>
       </x:c>
       <x:c r="R8" s="3" t="s">
         <x:v>52</x:v>
@@ -1430,10 +1430,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P9" s="0">
-        <x:v>49679</x:v>
+        <x:v>50163</x:v>
       </x:c>
       <x:c r="Q9" s="0">
-        <x:v>4004</x:v>
+        <x:v>4005</x:v>
       </x:c>
       <x:c r="R9" s="3" t="s">
         <x:v>52</x:v>
@@ -1486,10 +1486,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P10" s="0">
-        <x:v>4004</x:v>
+        <x:v>4005</x:v>
       </x:c>
       <x:c r="Q10" s="0">
-        <x:v>49679</x:v>
+        <x:v>50163</x:v>
       </x:c>
       <x:c r="R10" s="3" t="s">
         <x:v>52</x:v>

--- a/Hand_edited_log/1/student/dungtdhe186461/TC1/GradeDetail.xlsx
+++ b/Hand_edited_log/1/student/dungtdhe186461/TC1/GradeDetail.xlsx
@@ -1038,10 +1038,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P2" s="0">
-        <x:v>50163</x:v>
+        <x:v>61768</x:v>
       </x:c>
       <x:c r="Q2" s="0">
-        <x:v>4005</x:v>
+        <x:v>4000</x:v>
       </x:c>
       <x:c r="R2" s="2" t="s">
         <x:v>46</x:v>
@@ -1094,10 +1094,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P3" s="0">
-        <x:v>4005</x:v>
+        <x:v>4000</x:v>
       </x:c>
       <x:c r="Q3" s="0">
-        <x:v>50163</x:v>
+        <x:v>61768</x:v>
       </x:c>
       <x:c r="R3" s="2" t="s">
         <x:v>46</x:v>
@@ -1150,10 +1150,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P4" s="0">
-        <x:v>50163</x:v>
+        <x:v>61768</x:v>
       </x:c>
       <x:c r="Q4" s="0">
-        <x:v>4005</x:v>
+        <x:v>4000</x:v>
       </x:c>
       <x:c r="R4" s="3" t="s">
         <x:v>52</x:v>
@@ -1206,10 +1206,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P5" s="0">
-        <x:v>4005</x:v>
+        <x:v>4000</x:v>
       </x:c>
       <x:c r="Q5" s="0">
-        <x:v>50163</x:v>
+        <x:v>61768</x:v>
       </x:c>
       <x:c r="R5" s="3" t="s">
         <x:v>52</x:v>
@@ -1262,10 +1262,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P6" s="0">
-        <x:v>50163</x:v>
+        <x:v>61768</x:v>
       </x:c>
       <x:c r="Q6" s="0">
-        <x:v>4005</x:v>
+        <x:v>4000</x:v>
       </x:c>
       <x:c r="R6" s="3" t="s">
         <x:v>52</x:v>
@@ -1318,10 +1318,10 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="P7" s="0">
-        <x:v>50163</x:v>
+        <x:v>61768</x:v>
       </x:c>
       <x:c r="Q7" s="0">
-        <x:v>4005</x:v>
+        <x:v>4000</x:v>
       </x:c>
       <x:c r="R7" s="3" t="s">
         <x:v>52</x:v>
@@ -1374,10 +1374,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P8" s="0">
-        <x:v>4005</x:v>
+        <x:v>4000</x:v>
       </x:c>
       <x:c r="Q8" s="0">
-        <x:v>50163</x:v>
+        <x:v>61768</x:v>
       </x:c>
       <x:c r="R8" s="3" t="s">
         <x:v>52</x:v>
@@ -1430,10 +1430,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P9" s="0">
-        <x:v>50163</x:v>
+        <x:v>61768</x:v>
       </x:c>
       <x:c r="Q9" s="0">
-        <x:v>4005</x:v>
+        <x:v>4000</x:v>
       </x:c>
       <x:c r="R9" s="3" t="s">
         <x:v>52</x:v>
@@ -1486,10 +1486,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P10" s="0">
-        <x:v>4005</x:v>
+        <x:v>4000</x:v>
       </x:c>
       <x:c r="Q10" s="0">
-        <x:v>50163</x:v>
+        <x:v>61768</x:v>
       </x:c>
       <x:c r="R10" s="3" t="s">
         <x:v>52</x:v>

--- a/Hand_edited_log/1/student/dungtdhe186461/TC1/GradeDetail.xlsx
+++ b/Hand_edited_log/1/student/dungtdhe186461/TC1/GradeDetail.xlsx
@@ -1038,10 +1038,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P2" s="0">
-        <x:v>61768</x:v>
+        <x:v>52018</x:v>
       </x:c>
       <x:c r="Q2" s="0">
-        <x:v>4000</x:v>
+        <x:v>4005</x:v>
       </x:c>
       <x:c r="R2" s="2" t="s">
         <x:v>46</x:v>
@@ -1094,10 +1094,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P3" s="0">
-        <x:v>4000</x:v>
+        <x:v>4005</x:v>
       </x:c>
       <x:c r="Q3" s="0">
-        <x:v>61768</x:v>
+        <x:v>52018</x:v>
       </x:c>
       <x:c r="R3" s="2" t="s">
         <x:v>46</x:v>
@@ -1150,10 +1150,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P4" s="0">
-        <x:v>61768</x:v>
+        <x:v>52018</x:v>
       </x:c>
       <x:c r="Q4" s="0">
-        <x:v>4000</x:v>
+        <x:v>4005</x:v>
       </x:c>
       <x:c r="R4" s="3" t="s">
         <x:v>52</x:v>
@@ -1206,10 +1206,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P5" s="0">
-        <x:v>4000</x:v>
+        <x:v>4005</x:v>
       </x:c>
       <x:c r="Q5" s="0">
-        <x:v>61768</x:v>
+        <x:v>52018</x:v>
       </x:c>
       <x:c r="R5" s="3" t="s">
         <x:v>52</x:v>
@@ -1262,10 +1262,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P6" s="0">
-        <x:v>61768</x:v>
+        <x:v>52018</x:v>
       </x:c>
       <x:c r="Q6" s="0">
-        <x:v>4000</x:v>
+        <x:v>4005</x:v>
       </x:c>
       <x:c r="R6" s="3" t="s">
         <x:v>52</x:v>
@@ -1318,10 +1318,10 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="P7" s="0">
-        <x:v>61768</x:v>
+        <x:v>52018</x:v>
       </x:c>
       <x:c r="Q7" s="0">
-        <x:v>4000</x:v>
+        <x:v>4005</x:v>
       </x:c>
       <x:c r="R7" s="3" t="s">
         <x:v>52</x:v>
@@ -1374,10 +1374,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P8" s="0">
-        <x:v>4000</x:v>
+        <x:v>4005</x:v>
       </x:c>
       <x:c r="Q8" s="0">
-        <x:v>61768</x:v>
+        <x:v>52018</x:v>
       </x:c>
       <x:c r="R8" s="3" t="s">
         <x:v>52</x:v>
@@ -1430,10 +1430,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P9" s="0">
-        <x:v>61768</x:v>
+        <x:v>52018</x:v>
       </x:c>
       <x:c r="Q9" s="0">
-        <x:v>4000</x:v>
+        <x:v>4005</x:v>
       </x:c>
       <x:c r="R9" s="3" t="s">
         <x:v>52</x:v>
@@ -1486,10 +1486,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P10" s="0">
-        <x:v>4000</x:v>
+        <x:v>4005</x:v>
       </x:c>
       <x:c r="Q10" s="0">
-        <x:v>61768</x:v>
+        <x:v>52018</x:v>
       </x:c>
       <x:c r="R10" s="3" t="s">
         <x:v>52</x:v>

--- a/Hand_edited_log/1/student/dungtdhe186461/TC1/GradeDetail.xlsx
+++ b/Hand_edited_log/1/student/dungtdhe186461/TC1/GradeDetail.xlsx
@@ -1038,10 +1038,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P2" s="0">
-        <x:v>52018</x:v>
+        <x:v>59434</x:v>
       </x:c>
       <x:c r="Q2" s="0">
-        <x:v>4005</x:v>
+        <x:v>4000</x:v>
       </x:c>
       <x:c r="R2" s="2" t="s">
         <x:v>46</x:v>
@@ -1094,10 +1094,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P3" s="0">
-        <x:v>4005</x:v>
+        <x:v>4000</x:v>
       </x:c>
       <x:c r="Q3" s="0">
-        <x:v>52018</x:v>
+        <x:v>59434</x:v>
       </x:c>
       <x:c r="R3" s="2" t="s">
         <x:v>46</x:v>
@@ -1150,10 +1150,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P4" s="0">
-        <x:v>52018</x:v>
+        <x:v>59434</x:v>
       </x:c>
       <x:c r="Q4" s="0">
-        <x:v>4005</x:v>
+        <x:v>4000</x:v>
       </x:c>
       <x:c r="R4" s="3" t="s">
         <x:v>52</x:v>
@@ -1206,10 +1206,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P5" s="0">
-        <x:v>4005</x:v>
+        <x:v>4000</x:v>
       </x:c>
       <x:c r="Q5" s="0">
-        <x:v>52018</x:v>
+        <x:v>59434</x:v>
       </x:c>
       <x:c r="R5" s="3" t="s">
         <x:v>52</x:v>
@@ -1262,10 +1262,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P6" s="0">
-        <x:v>52018</x:v>
+        <x:v>59434</x:v>
       </x:c>
       <x:c r="Q6" s="0">
-        <x:v>4005</x:v>
+        <x:v>4000</x:v>
       </x:c>
       <x:c r="R6" s="3" t="s">
         <x:v>52</x:v>
@@ -1318,10 +1318,10 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="P7" s="0">
-        <x:v>52018</x:v>
+        <x:v>59434</x:v>
       </x:c>
       <x:c r="Q7" s="0">
-        <x:v>4005</x:v>
+        <x:v>4000</x:v>
       </x:c>
       <x:c r="R7" s="3" t="s">
         <x:v>52</x:v>
@@ -1374,10 +1374,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P8" s="0">
-        <x:v>4005</x:v>
+        <x:v>4000</x:v>
       </x:c>
       <x:c r="Q8" s="0">
-        <x:v>52018</x:v>
+        <x:v>59434</x:v>
       </x:c>
       <x:c r="R8" s="3" t="s">
         <x:v>52</x:v>
@@ -1430,10 +1430,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P9" s="0">
-        <x:v>52018</x:v>
+        <x:v>59434</x:v>
       </x:c>
       <x:c r="Q9" s="0">
-        <x:v>4005</x:v>
+        <x:v>4000</x:v>
       </x:c>
       <x:c r="R9" s="3" t="s">
         <x:v>52</x:v>
@@ -1486,10 +1486,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P10" s="0">
-        <x:v>4005</x:v>
+        <x:v>4000</x:v>
       </x:c>
       <x:c r="Q10" s="0">
-        <x:v>52018</x:v>
+        <x:v>59434</x:v>
       </x:c>
       <x:c r="R10" s="3" t="s">
         <x:v>52</x:v>

--- a/Hand_edited_log/1/student/dungtdhe186461/TC1/GradeDetail.xlsx
+++ b/Hand_edited_log/1/student/dungtdhe186461/TC1/GradeDetail.xlsx
@@ -1038,7 +1038,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P2" s="0">
-        <x:v>59434</x:v>
+        <x:v>51736</x:v>
       </x:c>
       <x:c r="Q2" s="0">
         <x:v>4000</x:v>
@@ -1097,7 +1097,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q3" s="0">
-        <x:v>59434</x:v>
+        <x:v>51736</x:v>
       </x:c>
       <x:c r="R3" s="2" t="s">
         <x:v>46</x:v>
@@ -1150,7 +1150,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P4" s="0">
-        <x:v>59434</x:v>
+        <x:v>51736</x:v>
       </x:c>
       <x:c r="Q4" s="0">
         <x:v>4000</x:v>
@@ -1209,7 +1209,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q5" s="0">
-        <x:v>59434</x:v>
+        <x:v>51736</x:v>
       </x:c>
       <x:c r="R5" s="3" t="s">
         <x:v>52</x:v>
@@ -1262,7 +1262,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P6" s="0">
-        <x:v>59434</x:v>
+        <x:v>51736</x:v>
       </x:c>
       <x:c r="Q6" s="0">
         <x:v>4000</x:v>
@@ -1318,7 +1318,7 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="P7" s="0">
-        <x:v>59434</x:v>
+        <x:v>51736</x:v>
       </x:c>
       <x:c r="Q7" s="0">
         <x:v>4000</x:v>
@@ -1377,7 +1377,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q8" s="0">
-        <x:v>59434</x:v>
+        <x:v>51736</x:v>
       </x:c>
       <x:c r="R8" s="3" t="s">
         <x:v>52</x:v>
@@ -1430,7 +1430,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P9" s="0">
-        <x:v>59434</x:v>
+        <x:v>51736</x:v>
       </x:c>
       <x:c r="Q9" s="0">
         <x:v>4000</x:v>
@@ -1489,7 +1489,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q10" s="0">
-        <x:v>59434</x:v>
+        <x:v>51736</x:v>
       </x:c>
       <x:c r="R10" s="3" t="s">
         <x:v>52</x:v>

--- a/Hand_edited_log/1/student/dungtdhe186461/TC1/GradeDetail.xlsx
+++ b/Hand_edited_log/1/student/dungtdhe186461/TC1/GradeDetail.xlsx
@@ -1038,7 +1038,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P2" s="0">
-        <x:v>51736</x:v>
+        <x:v>62598</x:v>
       </x:c>
       <x:c r="Q2" s="0">
         <x:v>4000</x:v>
@@ -1097,7 +1097,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q3" s="0">
-        <x:v>51736</x:v>
+        <x:v>62598</x:v>
       </x:c>
       <x:c r="R3" s="2" t="s">
         <x:v>46</x:v>
@@ -1150,7 +1150,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P4" s="0">
-        <x:v>51736</x:v>
+        <x:v>62598</x:v>
       </x:c>
       <x:c r="Q4" s="0">
         <x:v>4000</x:v>
@@ -1209,7 +1209,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q5" s="0">
-        <x:v>51736</x:v>
+        <x:v>62598</x:v>
       </x:c>
       <x:c r="R5" s="3" t="s">
         <x:v>52</x:v>
@@ -1262,7 +1262,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P6" s="0">
-        <x:v>51736</x:v>
+        <x:v>62598</x:v>
       </x:c>
       <x:c r="Q6" s="0">
         <x:v>4000</x:v>
@@ -1318,7 +1318,7 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="P7" s="0">
-        <x:v>51736</x:v>
+        <x:v>62598</x:v>
       </x:c>
       <x:c r="Q7" s="0">
         <x:v>4000</x:v>
@@ -1377,7 +1377,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q8" s="0">
-        <x:v>51736</x:v>
+        <x:v>62598</x:v>
       </x:c>
       <x:c r="R8" s="3" t="s">
         <x:v>52</x:v>
@@ -1430,7 +1430,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P9" s="0">
-        <x:v>51736</x:v>
+        <x:v>62598</x:v>
       </x:c>
       <x:c r="Q9" s="0">
         <x:v>4000</x:v>
@@ -1489,7 +1489,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q10" s="0">
-        <x:v>51736</x:v>
+        <x:v>62598</x:v>
       </x:c>
       <x:c r="R10" s="3" t="s">
         <x:v>52</x:v>

--- a/Hand_edited_log/1/student/dungtdhe186461/TC1/GradeDetail.xlsx
+++ b/Hand_edited_log/1/student/dungtdhe186461/TC1/GradeDetail.xlsx
@@ -1038,7 +1038,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P2" s="0">
-        <x:v>62598</x:v>
+        <x:v>64206</x:v>
       </x:c>
       <x:c r="Q2" s="0">
         <x:v>4000</x:v>
@@ -1097,7 +1097,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q3" s="0">
-        <x:v>62598</x:v>
+        <x:v>64206</x:v>
       </x:c>
       <x:c r="R3" s="2" t="s">
         <x:v>46</x:v>
@@ -1150,7 +1150,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P4" s="0">
-        <x:v>62598</x:v>
+        <x:v>64206</x:v>
       </x:c>
       <x:c r="Q4" s="0">
         <x:v>4000</x:v>
@@ -1209,7 +1209,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q5" s="0">
-        <x:v>62598</x:v>
+        <x:v>64206</x:v>
       </x:c>
       <x:c r="R5" s="3" t="s">
         <x:v>52</x:v>
@@ -1262,7 +1262,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P6" s="0">
-        <x:v>62598</x:v>
+        <x:v>64206</x:v>
       </x:c>
       <x:c r="Q6" s="0">
         <x:v>4000</x:v>
@@ -1318,7 +1318,7 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="P7" s="0">
-        <x:v>62598</x:v>
+        <x:v>64206</x:v>
       </x:c>
       <x:c r="Q7" s="0">
         <x:v>4000</x:v>
@@ -1377,7 +1377,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q8" s="0">
-        <x:v>62598</x:v>
+        <x:v>64206</x:v>
       </x:c>
       <x:c r="R8" s="3" t="s">
         <x:v>52</x:v>
@@ -1430,7 +1430,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P9" s="0">
-        <x:v>62598</x:v>
+        <x:v>64206</x:v>
       </x:c>
       <x:c r="Q9" s="0">
         <x:v>4000</x:v>
@@ -1489,7 +1489,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q10" s="0">
-        <x:v>62598</x:v>
+        <x:v>64206</x:v>
       </x:c>
       <x:c r="R10" s="3" t="s">
         <x:v>52</x:v>

--- a/Hand_edited_log/1/student/dungtdhe186461/TC1/GradeDetail.xlsx
+++ b/Hand_edited_log/1/student/dungtdhe186461/TC1/GradeDetail.xlsx
@@ -1038,7 +1038,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P2" s="0">
-        <x:v>64206</x:v>
+        <x:v>60118</x:v>
       </x:c>
       <x:c r="Q2" s="0">
         <x:v>4000</x:v>
@@ -1097,7 +1097,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q3" s="0">
-        <x:v>64206</x:v>
+        <x:v>60118</x:v>
       </x:c>
       <x:c r="R3" s="2" t="s">
         <x:v>46</x:v>
@@ -1150,7 +1150,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P4" s="0">
-        <x:v>64206</x:v>
+        <x:v>60118</x:v>
       </x:c>
       <x:c r="Q4" s="0">
         <x:v>4000</x:v>
@@ -1209,7 +1209,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q5" s="0">
-        <x:v>64206</x:v>
+        <x:v>60118</x:v>
       </x:c>
       <x:c r="R5" s="3" t="s">
         <x:v>52</x:v>
@@ -1262,7 +1262,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P6" s="0">
-        <x:v>64206</x:v>
+        <x:v>60118</x:v>
       </x:c>
       <x:c r="Q6" s="0">
         <x:v>4000</x:v>
@@ -1318,7 +1318,7 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="P7" s="0">
-        <x:v>64206</x:v>
+        <x:v>60118</x:v>
       </x:c>
       <x:c r="Q7" s="0">
         <x:v>4000</x:v>
@@ -1377,7 +1377,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q8" s="0">
-        <x:v>64206</x:v>
+        <x:v>60118</x:v>
       </x:c>
       <x:c r="R8" s="3" t="s">
         <x:v>52</x:v>
@@ -1430,7 +1430,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P9" s="0">
-        <x:v>64206</x:v>
+        <x:v>60118</x:v>
       </x:c>
       <x:c r="Q9" s="0">
         <x:v>4000</x:v>
@@ -1489,7 +1489,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q10" s="0">
-        <x:v>64206</x:v>
+        <x:v>60118</x:v>
       </x:c>
       <x:c r="R10" s="3" t="s">
         <x:v>52</x:v>

--- a/Hand_edited_log/1/student/dungtdhe186461/TC1/GradeDetail.xlsx
+++ b/Hand_edited_log/1/student/dungtdhe186461/TC1/GradeDetail.xlsx
@@ -1038,7 +1038,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P2" s="0">
-        <x:v>60118</x:v>
+        <x:v>49162</x:v>
       </x:c>
       <x:c r="Q2" s="0">
         <x:v>4000</x:v>
@@ -1097,7 +1097,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q3" s="0">
-        <x:v>60118</x:v>
+        <x:v>49162</x:v>
       </x:c>
       <x:c r="R3" s="2" t="s">
         <x:v>46</x:v>
@@ -1150,7 +1150,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P4" s="0">
-        <x:v>60118</x:v>
+        <x:v>49162</x:v>
       </x:c>
       <x:c r="Q4" s="0">
         <x:v>4000</x:v>
@@ -1209,7 +1209,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q5" s="0">
-        <x:v>60118</x:v>
+        <x:v>49162</x:v>
       </x:c>
       <x:c r="R5" s="3" t="s">
         <x:v>52</x:v>
@@ -1262,7 +1262,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P6" s="0">
-        <x:v>60118</x:v>
+        <x:v>49162</x:v>
       </x:c>
       <x:c r="Q6" s="0">
         <x:v>4000</x:v>
@@ -1318,7 +1318,7 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="P7" s="0">
-        <x:v>60118</x:v>
+        <x:v>49162</x:v>
       </x:c>
       <x:c r="Q7" s="0">
         <x:v>4000</x:v>
@@ -1377,7 +1377,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q8" s="0">
-        <x:v>60118</x:v>
+        <x:v>49162</x:v>
       </x:c>
       <x:c r="R8" s="3" t="s">
         <x:v>52</x:v>
@@ -1430,7 +1430,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P9" s="0">
-        <x:v>60118</x:v>
+        <x:v>49162</x:v>
       </x:c>
       <x:c r="Q9" s="0">
         <x:v>4000</x:v>
@@ -1489,7 +1489,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q10" s="0">
-        <x:v>60118</x:v>
+        <x:v>49162</x:v>
       </x:c>
       <x:c r="R10" s="3" t="s">
         <x:v>52</x:v>

--- a/Hand_edited_log/1/student/dungtdhe186461/TC1/GradeDetail.xlsx
+++ b/Hand_edited_log/1/student/dungtdhe186461/TC1/GradeDetail.xlsx
@@ -1038,7 +1038,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P2" s="0">
-        <x:v>49162</x:v>
+        <x:v>54226</x:v>
       </x:c>
       <x:c r="Q2" s="0">
         <x:v>4000</x:v>
@@ -1097,7 +1097,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q3" s="0">
-        <x:v>49162</x:v>
+        <x:v>54226</x:v>
       </x:c>
       <x:c r="R3" s="2" t="s">
         <x:v>46</x:v>
@@ -1150,7 +1150,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P4" s="0">
-        <x:v>49162</x:v>
+        <x:v>54226</x:v>
       </x:c>
       <x:c r="Q4" s="0">
         <x:v>4000</x:v>
@@ -1209,7 +1209,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q5" s="0">
-        <x:v>49162</x:v>
+        <x:v>54226</x:v>
       </x:c>
       <x:c r="R5" s="3" t="s">
         <x:v>52</x:v>
@@ -1262,7 +1262,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P6" s="0">
-        <x:v>49162</x:v>
+        <x:v>54226</x:v>
       </x:c>
       <x:c r="Q6" s="0">
         <x:v>4000</x:v>
@@ -1318,7 +1318,7 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="P7" s="0">
-        <x:v>49162</x:v>
+        <x:v>54226</x:v>
       </x:c>
       <x:c r="Q7" s="0">
         <x:v>4000</x:v>
@@ -1377,7 +1377,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q8" s="0">
-        <x:v>49162</x:v>
+        <x:v>54226</x:v>
       </x:c>
       <x:c r="R8" s="3" t="s">
         <x:v>52</x:v>
@@ -1430,7 +1430,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P9" s="0">
-        <x:v>49162</x:v>
+        <x:v>54226</x:v>
       </x:c>
       <x:c r="Q9" s="0">
         <x:v>4000</x:v>
@@ -1489,7 +1489,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q10" s="0">
-        <x:v>49162</x:v>
+        <x:v>54226</x:v>
       </x:c>
       <x:c r="R10" s="3" t="s">
         <x:v>52</x:v>

--- a/Hand_edited_log/1/student/dungtdhe186461/TC1/GradeDetail.xlsx
+++ b/Hand_edited_log/1/student/dungtdhe186461/TC1/GradeDetail.xlsx
@@ -1038,7 +1038,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P2" s="0">
-        <x:v>54226</x:v>
+        <x:v>56513</x:v>
       </x:c>
       <x:c r="Q2" s="0">
         <x:v>4000</x:v>
@@ -1097,7 +1097,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q3" s="0">
-        <x:v>54226</x:v>
+        <x:v>56513</x:v>
       </x:c>
       <x:c r="R3" s="2" t="s">
         <x:v>46</x:v>
@@ -1150,7 +1150,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P4" s="0">
-        <x:v>54226</x:v>
+        <x:v>56513</x:v>
       </x:c>
       <x:c r="Q4" s="0">
         <x:v>4000</x:v>
@@ -1209,7 +1209,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q5" s="0">
-        <x:v>54226</x:v>
+        <x:v>56513</x:v>
       </x:c>
       <x:c r="R5" s="3" t="s">
         <x:v>52</x:v>
@@ -1262,7 +1262,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P6" s="0">
-        <x:v>54226</x:v>
+        <x:v>56513</x:v>
       </x:c>
       <x:c r="Q6" s="0">
         <x:v>4000</x:v>
@@ -1318,7 +1318,7 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="P7" s="0">
-        <x:v>54226</x:v>
+        <x:v>56513</x:v>
       </x:c>
       <x:c r="Q7" s="0">
         <x:v>4000</x:v>
@@ -1377,7 +1377,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q8" s="0">
-        <x:v>54226</x:v>
+        <x:v>56513</x:v>
       </x:c>
       <x:c r="R8" s="3" t="s">
         <x:v>52</x:v>
@@ -1430,7 +1430,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P9" s="0">
-        <x:v>54226</x:v>
+        <x:v>56513</x:v>
       </x:c>
       <x:c r="Q9" s="0">
         <x:v>4000</x:v>
@@ -1489,7 +1489,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q10" s="0">
-        <x:v>54226</x:v>
+        <x:v>56513</x:v>
       </x:c>
       <x:c r="R10" s="3" t="s">
         <x:v>52</x:v>

--- a/Hand_edited_log/1/student/dungtdhe186461/TC1/GradeDetail.xlsx
+++ b/Hand_edited_log/1/student/dungtdhe186461/TC1/GradeDetail.xlsx
@@ -1038,7 +1038,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P2" s="0">
-        <x:v>56513</x:v>
+        <x:v>61471</x:v>
       </x:c>
       <x:c r="Q2" s="0">
         <x:v>4000</x:v>
@@ -1097,7 +1097,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q3" s="0">
-        <x:v>56513</x:v>
+        <x:v>61471</x:v>
       </x:c>
       <x:c r="R3" s="2" t="s">
         <x:v>46</x:v>
@@ -1150,7 +1150,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P4" s="0">
-        <x:v>56513</x:v>
+        <x:v>61471</x:v>
       </x:c>
       <x:c r="Q4" s="0">
         <x:v>4000</x:v>
@@ -1209,7 +1209,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q5" s="0">
-        <x:v>56513</x:v>
+        <x:v>61471</x:v>
       </x:c>
       <x:c r="R5" s="3" t="s">
         <x:v>52</x:v>
@@ -1262,7 +1262,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P6" s="0">
-        <x:v>56513</x:v>
+        <x:v>61471</x:v>
       </x:c>
       <x:c r="Q6" s="0">
         <x:v>4000</x:v>
@@ -1318,7 +1318,7 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="P7" s="0">
-        <x:v>56513</x:v>
+        <x:v>61471</x:v>
       </x:c>
       <x:c r="Q7" s="0">
         <x:v>4000</x:v>
@@ -1377,7 +1377,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q8" s="0">
-        <x:v>56513</x:v>
+        <x:v>61471</x:v>
       </x:c>
       <x:c r="R8" s="3" t="s">
         <x:v>52</x:v>
@@ -1430,7 +1430,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P9" s="0">
-        <x:v>56513</x:v>
+        <x:v>61471</x:v>
       </x:c>
       <x:c r="Q9" s="0">
         <x:v>4000</x:v>
@@ -1489,7 +1489,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q10" s="0">
-        <x:v>56513</x:v>
+        <x:v>61471</x:v>
       </x:c>
       <x:c r="R10" s="3" t="s">
         <x:v>52</x:v>
